--- a/egg_production.xlsx
+++ b/egg_production.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lmigov.sharepoint.us/sites/LMICodingChallenge_Group/Shared Documents/General/Spring 2026/Week 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miles.exner/Development/tmyc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_09474C4F2737C2E3A6E451F959F6E696580667D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21E9614D-8EC1-45C3-B780-F75CB4CB73F6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED595CD-309A-4F44-AE2A-D89A932AB894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pastel" sheetId="1" r:id="rId1"/>
@@ -471,15 +471,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -490,7 +490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -505,7 +505,7 @@
         <v>3.3005617977528087E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -520,7 +520,7 @@
         <v>3.1890660592255128E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -535,7 +535,7 @@
         <v>2.6712328767123289E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -550,7 +550,7 @@
         <v>3.5254237288135593E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -565,7 +565,7 @@
         <v>2.9742765273311898E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -580,7 +580,7 @@
         <v>1.9290123456790122E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -595,7 +595,7 @@
         <v>2.9078014184397163E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -610,7 +610,7 @@
         <v>1.8181818181818181E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -625,7 +625,7 @@
         <v>3.2880629020729094E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -640,14 +640,9 @@
         <v>2.5525525525525526E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="D15">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D11">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>0.03</formula>
     </cfRule>
   </conditionalFormatting>
@@ -657,15 +652,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -676,7 +671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -691,7 +686,7 @@
         <v>5.2875695732838589E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -706,7 +701,7 @@
         <v>2.6522593320235755E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -721,7 +716,7 @@
         <v>2.566158781074579E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -736,7 +731,7 @@
         <v>2.3126734505087881E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -751,7 +746,7 @@
         <v>3.7178265014299335E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -766,7 +761,7 @@
         <v>4.2533081285444231E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -781,7 +776,7 @@
         <v>3.006872852233677E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -796,7 +791,7 @@
         <v>2.2727272727272728E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -811,7 +806,7 @@
         <v>2.2608695652173914E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -824,11 +819,6 @@
       <c r="D11">
         <f t="shared" si="0"/>
         <v>3.7326388888888888E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D17">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -843,15 +833,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -862,7 +852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -877,7 +867,7 @@
         <v>2.433862433862434E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -892,7 +882,7 @@
         <v>2.6795284030010719E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -907,7 +897,7 @@
         <v>1.1627906976744186E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -922,7 +912,7 @@
         <v>1.9693654266958426E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -937,7 +927,7 @@
         <v>1.8743109151047408E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -952,7 +942,7 @@
         <v>1.7524644030668127E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -967,7 +957,7 @@
         <v>1.9957983193277309E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -982,7 +972,7 @@
         <v>3.2858707557502739E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -997,7 +987,7 @@
         <v>1.5940488841657812E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1012,14 +1002,9 @@
         <v>2.8761061946902654E-2</v>
       </c>
     </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D20">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D11">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.03</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1039,6 +1024,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E54BDBC1D4EADA4AB5098F3D046673FB" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d226c54637869e00d2aa04e35a4931ee">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3b401470-3d21-454c-b83f-2f4f030ecb89" xmlns:ns3="2f5df6f9-da7c-4393-acd9-741c78b76444" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4c1ceb970b1cc38b3944981ea9c24889" ns2:_="" ns3:_="">
     <xsd:import namespace="3b401470-3d21-454c-b83f-2f4f030ecb89"/>
@@ -1273,15 +1267,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4658A8EE-61A6-4A1C-A954-075512A0DEFE}">
   <ds:schemaRefs>
@@ -1300,6 +1285,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E239FC1-85F0-4271-B6F0-6147A5EAEA44}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5C6D357-93A4-4E01-8645-C57B5A06092E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1316,12 +1309,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E239FC1-85F0-4271-B6F0-6147A5EAEA44}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>